--- a/Convert_from_xlsx_to_Json/table_normalization/economy-table76.xlsx
+++ b/Convert_from_xlsx_to_Json/table_normalization/economy-table76.xlsx
@@ -82,8 +82,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="2">
-    <numFmt numFmtId="167" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="168" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="165" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -116,7 +116,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -125,19 +125,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF00B050"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00B0F0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -164,14 +152,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -180,20 +168,19 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="168" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="168" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="168" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Денежный" xfId="1" builtinId="4"/>
@@ -683,80 +670,80 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15.5">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1"/>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="9" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="15.5">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="3"/>
-      <c r="C2" s="4">
+      <c r="C2" s="10">
         <v>52500</v>
       </c>
-      <c r="D2" s="4">
+      <c r="D2" s="10">
         <v>52500</v>
       </c>
-      <c r="E2" s="4">
+      <c r="E2" s="10">
         <f>C2+D2</f>
         <v>105000</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="15.5">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B3" s="3"/>
-      <c r="C3" s="4">
+      <c r="C3" s="10">
         <v>550000</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D3" s="10">
         <v>550000</v>
       </c>
-      <c r="E3" s="4">
+      <c r="E3" s="10">
         <f>D3+C3</f>
         <v>1100000</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="15.5">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="3"/>
-      <c r="C4" s="4">
+      <c r="C4" s="10">
         <v>150000</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="10">
         <v>150000</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E4" s="10">
         <f>D4+C4</f>
         <v>300000</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15.5">
-      <c r="A5" s="9" t="s">
+      <c r="A5" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B5" s="3"/>
-      <c r="C5" s="5">
+      <c r="C5" s="11">
         <v>5000</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D5" s="11">
         <v>5000</v>
       </c>
-      <c r="E5" s="5">
+      <c r="E5" s="11">
         <f>D5+C5</f>
         <v>10000</v>
       </c>
@@ -766,83 +753,83 @@
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
-      <c r="E6" s="4"/>
+      <c r="E6" s="10"/>
     </row>
     <row r="7" spans="1:5" ht="15.5">
-      <c r="A7" s="11" t="s">
+      <c r="A7" s="8" t="s">
         <v>8</v>
       </c>
       <c r="B7" s="3"/>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" s="9" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="15.5">
-      <c r="A8" s="9" t="s">
+      <c r="A8" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B8" s="3"/>
-      <c r="C8" s="4">
+      <c r="C8" s="10">
         <v>550000</v>
       </c>
-      <c r="D8" s="4">
+      <c r="D8" s="10">
         <v>550000</v>
       </c>
-      <c r="E8" s="4">
+      <c r="E8" s="10">
         <f t="shared" ref="E8:E10" si="0">SUM(C8:D8)</f>
         <v>1100000</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="15.5">
-      <c r="A9" s="9" t="s">
+      <c r="A9" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B9" s="3"/>
-      <c r="C9" s="4">
+      <c r="C9" s="10">
         <v>150000</v>
       </c>
-      <c r="D9" s="4">
+      <c r="D9" s="10">
         <v>150000</v>
       </c>
-      <c r="E9" s="4">
+      <c r="E9" s="10">
         <f t="shared" si="0"/>
         <v>300000</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="15.5">
-      <c r="A10" s="9" t="s">
+      <c r="A10" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B10" s="3"/>
-      <c r="C10" s="4">
+      <c r="C10" s="10">
         <v>100000</v>
       </c>
-      <c r="D10" s="4">
+      <c r="D10" s="10">
         <v>100000</v>
       </c>
-      <c r="E10" s="4">
+      <c r="E10" s="10">
         <f t="shared" si="0"/>
         <v>200000</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="15.5">
-      <c r="A11" s="9" t="s">
+      <c r="A11" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B11" s="3"/>
-      <c r="C11" s="6">
+      <c r="C11" s="12">
         <v>1</v>
       </c>
-      <c r="D11" s="6">
+      <c r="D11" s="12">
         <v>1</v>
       </c>
-      <c r="E11" s="5"/>
+      <c r="E11" s="11"/>
     </row>
     <row r="12" spans="1:5" ht="15.5">
       <c r="A12" s="3"/>
@@ -852,40 +839,40 @@
       <c r="E12" s="3"/>
     </row>
     <row r="13" spans="1:5" ht="15.5">
-      <c r="A13" s="11" t="s">
+      <c r="A13" s="8" t="s">
         <v>11</v>
       </c>
       <c r="B13" s="3"/>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="D13" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="E13" s="8" t="s">
+      <c r="E13" s="9" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="15.5">
-      <c r="A14" s="9" t="s">
+      <c r="A14" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B14" s="3"/>
-      <c r="C14" s="7">
+      <c r="C14" s="6">
         <f>C2</f>
         <v>52500</v>
       </c>
-      <c r="D14" s="7">
+      <c r="D14" s="6">
         <f>D2</f>
         <v>52500</v>
       </c>
-      <c r="E14" s="7">
+      <c r="E14" s="6">
         <f>E2</f>
         <v>105000</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="15.5">
-      <c r="A15" s="9" t="s">
+      <c r="A15" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B15" s="3"/>
@@ -903,7 +890,7 @@
       </c>
     </row>
     <row r="16" spans="1:5" ht="15.5">
-      <c r="A16" s="9" t="s">
+      <c r="A16" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B16" s="3"/>
@@ -921,7 +908,7 @@
       </c>
     </row>
     <row r="17" spans="1:5" ht="15.5">
-      <c r="A17" s="9" t="s">
+      <c r="A17" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B17" s="3"/>
@@ -939,7 +926,7 @@
       </c>
     </row>
     <row r="18" spans="1:5" ht="15.5">
-      <c r="A18" s="9" t="s">
+      <c r="A18" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B18" s="3"/>
@@ -957,19 +944,19 @@
       </c>
     </row>
     <row r="19" spans="1:5" ht="15.5">
-      <c r="A19" s="10" t="s">
+      <c r="A19" s="7" t="s">
         <v>15</v>
       </c>
       <c r="B19" s="3"/>
-      <c r="C19" s="7">
+      <c r="C19" s="6">
         <f>SUM(C14:C18)</f>
         <v>70000</v>
       </c>
-      <c r="D19" s="7">
+      <c r="D19" s="6">
         <f>SUM(D14:D18)</f>
         <v>70000</v>
       </c>
-      <c r="E19" s="7">
+      <c r="E19" s="6">
         <f>SUM(E14:E18)</f>
         <v>140000</v>
       </c>
